--- a/User Stories & Sprint Backlog.xlsx
+++ b/User Stories & Sprint Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amark\OneDrive\Desktop\HCL\Credit Card Fraud Detection Using Anomaly Detection Techniques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA12162-1124-4656-9A22-784511896CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5016CBD3-399C-49BD-B484-5C8AD1E93B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F41CDA0A-0E34-43A3-8B59-BE7BC0731DAE}"/>
   </bookViews>
